--- a/sources/1F_Tarde_1_Bimestre.xlsx
+++ b/sources/1F_Tarde_1_Bimestre.xlsx
@@ -290,6 +290,15 @@
     <x:t>EMILLY BRAGA VIEIRA</x:t>
   </x:si>
   <x:si>
+    <x:t>FABRÍCIO HOLANDA SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>100%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0%</x:t>
+  </x:si>
+  <x:si>
     <x:t>GABRIELLY DIAS IGLESIAS</x:t>
   </x:si>
   <x:si>
@@ -317,6 +326,9 @@
     <x:t>82%</x:t>
   </x:si>
   <x:si>
+    <x:t>ISABELLY APARECIDA BATISTA DA SILVA</x:t>
+  </x:si>
+  <x:si>
     <x:t>ISABELLY SCAGLIA BARASINO</x:t>
   </x:si>
   <x:si>
@@ -326,9 +338,6 @@
     <x:t>JENIFFER MACIEL DOS SANTOS</x:t>
   </x:si>
   <x:si>
-    <x:t>100%</x:t>
-  </x:si>
-  <x:si>
     <x:t>JHOSELYN RAMOS CHURA</x:t>
   </x:si>
   <x:si>
@@ -338,12 +347,15 @@
     <x:t>JHULIOS CESAR FRANCISCO DOS SANTOS BORGES</x:t>
   </x:si>
   <x:si>
-    <x:t>JOAO VICTOR CANDIDO BANDEIRA</x:t>
+    <x:t>JOÃO VICTOR CANDIDO BANDEIRA</x:t>
   </x:si>
   <x:si>
     <x:t>91%</x:t>
   </x:si>
   <x:si>
+    <x:t>JULIA BEATRIZ ARAUJO DA SILVA</x:t>
+  </x:si>
+  <x:si>
     <x:t>JULIA CORREIA MATIAS</x:t>
   </x:si>
   <x:si>
@@ -356,6 +368,15 @@
     <x:t>99%</x:t>
   </x:si>
   <x:si>
+    <x:t>KAUAN DA SILVA ESTEVÃO SOARES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LAIS SOPHIA PAULETI DOS SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LARISSA BRITO SEPULVEDA</x:t>
+  </x:si>
+  <x:si>
     <x:t>LAURA NICOLE DA SILVA</x:t>
   </x:si>
   <x:si>
@@ -422,6 +443,9 @@
     <x:t>MATHEUS VINYCIOS VILARES DA SILVA</x:t>
   </x:si>
   <x:si>
+    <x:t>NATHALLY CHRISTINA ALVES DE SOUZA</x:t>
+  </x:si>
+  <x:si>
     <x:t>NATHALY DA SILVA MARTINS</x:t>
   </x:si>
   <x:si>
@@ -450,30 +474,6 @@
   </x:si>
   <x:si>
     <x:t>WILLIAM MURILLO MENDOZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAUAN DA SILVA ESTEVÃO SOARES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JULIA BEATRIZ ARAUJO DA SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NATHALLY CHRISTINA ALVES DE SOUZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LARISSA BRITO SEPULVEDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISABELLY APARECIDA BATISTA DA SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FABRÍCIO HOLANDA SANTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LAIS SOPHIA PAULETI DOS SANTOS</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve"> </x:t>
@@ -3882,25 +3882,25 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D27" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E27" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F27" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="H27" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I27" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J27" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K27" s="12">
         <x:v>15</x:v>
@@ -3918,138 +3918,138 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="P27" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q27" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="R27" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="S27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="T27" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U27" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="V27" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="W27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="X27" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y27" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Z27" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AA27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="AB27" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC27" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AD27" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AE27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="AF27" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AG27" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AH27" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AI27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="AJ27" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK27" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AL27" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AM27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="AN27" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO27" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP27" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="AR27" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS27" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AT27" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AU27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="AV27" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW27" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AX27" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AY27" s="12">
         <x:v>15</x:v>
       </x:c>
       <x:c r="AZ27" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BA27" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BB27" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BC27" s="12">
-        <x:v>77</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BD27" s="12" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="BE27" s="12">
-        <x:v>77</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BF27" s="12" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:58">
       <x:c r="A28" s="11" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B28" s="12" t="s">
         <x:v>46</x:v>
@@ -4058,10 +4058,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="D28" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E28" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F28" s="12" t="s">
         <x:v>49</x:v>
@@ -4070,10 +4070,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H28" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I28" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J28" s="12" t="s">
         <x:v>49</x:v>
@@ -4094,10 +4094,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="P28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q28" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="R28" s="12" t="s">
         <x:v>49</x:v>
@@ -4109,7 +4109,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="U28" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="V28" s="12" t="s">
         <x:v>49</x:v>
@@ -4118,22 +4118,22 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="X28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Y28" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Z28" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AA28" s="12">
         <x:v>16</x:v>
       </x:c>
       <x:c r="AB28" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AC28" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AD28" s="12" t="s">
         <x:v>49</x:v>
@@ -4142,10 +4142,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AF28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="AG28" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AH28" s="12" t="s">
         <x:v>49</x:v>
@@ -4154,10 +4154,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AJ28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK28" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AL28" s="12" t="s">
         <x:v>49</x:v>
@@ -4166,10 +4166,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AN28" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AO28" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="AP28" s="12" t="s">
         <x:v>49</x:v>
@@ -4178,10 +4178,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AR28" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AS28" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="AT28" s="12" t="s">
         <x:v>49</x:v>
@@ -4190,10 +4190,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AV28" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AW28" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AX28" s="12" t="s">
         <x:v>49</x:v>
@@ -4202,30 +4202,30 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AZ28" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BA28" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BB28" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC28" s="12">
-        <x:v>11</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="BD28" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="BE28" s="12">
-        <x:v>9</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="BF28" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:58">
       <x:c r="A29" s="11" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B29" s="12" t="s">
         <x:v>46</x:v>
@@ -4234,10 +4234,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="D29" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E29" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F29" s="12" t="s">
         <x:v>49</x:v>
@@ -4246,10 +4246,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="H29" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="I29" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J29" s="12" t="s">
         <x:v>49</x:v>
@@ -4270,10 +4270,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P29" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q29" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R29" s="12" t="s">
         <x:v>49</x:v>
@@ -4282,10 +4282,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="T29" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U29" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V29" s="12" t="s">
         <x:v>49</x:v>
@@ -4294,22 +4294,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="X29" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Y29" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z29" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AA29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="AB29" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="AC29" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD29" s="12" t="s">
         <x:v>49</x:v>
@@ -4318,10 +4318,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AF29" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG29" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH29" s="12" t="s">
         <x:v>49</x:v>
@@ -4330,10 +4330,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AJ29" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK29" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL29" s="12" t="s">
         <x:v>49</x:v>
@@ -4342,10 +4342,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AN29" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO29" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AP29" s="12" t="s">
         <x:v>49</x:v>
@@ -4354,22 +4354,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AR29" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AS29" s="12" t="s">
-        <x:v>91</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT29" s="12" t="s">
-        <x:v>91</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU29" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="AV29" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="AW29" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AX29" s="12" t="s">
         <x:v>49</x:v>
@@ -4378,25 +4378,25 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AZ29" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BA29" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB29" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC29" s="12">
-        <x:v>89</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="BD29" s="12" t="s">
-        <x:v>92</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="BE29" s="12">
-        <x:v>66</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="BF29" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:58">
@@ -4404,16 +4404,16 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B30" s="12" t="s">
-        <x:v>94</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C30" s="12">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E30" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F30" s="12" t="s">
         <x:v>49</x:v>
@@ -4422,7 +4422,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="H30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I30" s="12" t="s">
         <x:v>51</x:v>
@@ -4446,10 +4446,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="P30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Q30" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="R30" s="12" t="s">
         <x:v>49</x:v>
@@ -4458,10 +4458,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="T30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="U30" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="V30" s="12" t="s">
         <x:v>49</x:v>
@@ -4470,22 +4470,22 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="X30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Y30" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Z30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AA30" s="12">
         <x:v>18</x:v>
       </x:c>
       <x:c r="AB30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AD30" s="12" t="s">
         <x:v>49</x:v>
@@ -4494,7 +4494,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AF30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AG30" s="12" t="s">
         <x:v>57</x:v>
@@ -4506,10 +4506,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AJ30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK30" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AL30" s="12" t="s">
         <x:v>49</x:v>
@@ -4518,10 +4518,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AN30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AO30" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AP30" s="12" t="s">
         <x:v>49</x:v>
@@ -4530,22 +4530,22 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AR30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AS30" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="AT30" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="AU30" s="12">
         <x:v>18</x:v>
       </x:c>
       <x:c r="AV30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AW30" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AX30" s="12" t="s">
         <x:v>49</x:v>
@@ -4554,7 +4554,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AZ30" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BA30" s="12" t="s">
         <x:v>57</x:v>
@@ -4563,16 +4563,16 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC30" s="12">
-        <x:v>51</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="BD30" s="12" t="s">
         <x:v>95</x:v>
       </x:c>
       <x:c r="BE30" s="12">
-        <x:v>51</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="BF30" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:58">
@@ -4580,16 +4580,16 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B31" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D31" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E31" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F31" s="12" t="s">
         <x:v>49</x:v>
@@ -4598,10 +4598,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="H31" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I31" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J31" s="12" t="s">
         <x:v>49</x:v>
@@ -4622,10 +4622,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="P31" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q31" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="R31" s="12" t="s">
         <x:v>49</x:v>
@@ -4634,10 +4634,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="T31" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U31" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="V31" s="12" t="s">
         <x:v>49</x:v>
@@ -4646,19 +4646,19 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="X31" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y31" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Z31" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AA31" s="12">
         <x:v>19</x:v>
       </x:c>
       <x:c r="AB31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AC31" s="12" t="s">
         <x:v>49</x:v>
@@ -4670,10 +4670,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AF31" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AG31" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AH31" s="12" t="s">
         <x:v>49</x:v>
@@ -4682,10 +4682,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AJ31" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK31" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AL31" s="12" t="s">
         <x:v>49</x:v>
@@ -4694,10 +4694,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AN31" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO31" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP31" s="12" t="s">
         <x:v>49</x:v>
@@ -4706,10 +4706,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AR31" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS31" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="AT31" s="12" t="s">
         <x:v>49</x:v>
@@ -4718,7 +4718,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AV31" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW31" s="12" t="s">
         <x:v>58</x:v>
@@ -4730,30 +4730,30 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AZ31" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BA31" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BB31" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC31" s="12">
-        <x:v>6</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BD31" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="BE31" s="12">
-        <x:v>5</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BF31" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:58">
       <x:c r="A32" s="11" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B32" s="12" t="s">
         <x:v>46</x:v>
@@ -4762,25 +4762,25 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D32" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F32" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="H32" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I32" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J32" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K32" s="12">
         <x:v>20</x:v>
@@ -4798,147 +4798,147 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="P32" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q32" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="R32" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="S32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="T32" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U32" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="V32" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="W32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="X32" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y32" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Z32" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AA32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="AB32" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC32" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AD32" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AE32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="AF32" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AG32" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AH32" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AI32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="AJ32" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK32" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AL32" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AM32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="AN32" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO32" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP32" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="AR32" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS32" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AT32" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AU32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="AV32" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW32" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AX32" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AY32" s="12">
         <x:v>20</x:v>
       </x:c>
       <x:c r="AZ32" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BA32" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BB32" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BC32" s="12">
-        <x:v>32</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BD32" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="BE32" s="12">
-        <x:v>32</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BF32" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:58">
       <x:c r="A33" s="11" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B33" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C33" s="12">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D33" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E33" s="12" t="s">
         <x:v>49</x:v>
@@ -4950,7 +4950,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="H33" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="I33" s="12" t="s">
         <x:v>49</x:v>
@@ -4974,10 +4974,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="P33" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Q33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="R33" s="12" t="s">
         <x:v>49</x:v>
@@ -4986,7 +4986,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="T33" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U33" s="12" t="s">
         <x:v>49</x:v>
@@ -4998,19 +4998,19 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="X33" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Y33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Z33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AA33" s="12">
         <x:v>21</x:v>
       </x:c>
       <x:c r="AB33" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AC33" s="12" t="s">
         <x:v>49</x:v>
@@ -5022,7 +5022,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AF33" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG33" s="12" t="s">
         <x:v>49</x:v>
@@ -5034,7 +5034,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AJ33" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK33" s="12" t="s">
         <x:v>49</x:v>
@@ -5046,7 +5046,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AN33" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO33" s="12" t="s">
         <x:v>49</x:v>
@@ -5058,7 +5058,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AR33" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AS33" s="12" t="s">
         <x:v>49</x:v>
@@ -5070,10 +5070,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AV33" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AW33" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AX33" s="12" t="s">
         <x:v>49</x:v>
@@ -5082,7 +5082,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AZ33" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="BA33" s="12" t="s">
         <x:v>49</x:v>
@@ -5091,33 +5091,33 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC33" s="12">
-        <x:v>0</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="BD33" s="12" t="s">
-        <x:v>99</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="BE33" s="12">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="BF33" s="12" t="s">
-        <x:v>99</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:58">
       <x:c r="A34" s="11" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B34" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C34" s="12">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E34" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F34" s="12" t="s">
         <x:v>49</x:v>
@@ -5126,10 +5126,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="H34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I34" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J34" s="12" t="s">
         <x:v>49</x:v>
@@ -5150,7 +5150,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="P34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Q34" s="12" t="s">
         <x:v>57</x:v>
@@ -5162,10 +5162,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="T34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U34" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="V34" s="12" t="s">
         <x:v>49</x:v>
@@ -5174,10 +5174,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="X34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Y34" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Z34" s="12" t="s">
         <x:v>49</x:v>
@@ -5186,10 +5186,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AB34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AC34" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AD34" s="12" t="s">
         <x:v>49</x:v>
@@ -5198,10 +5198,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AF34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG34" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AH34" s="12" t="s">
         <x:v>49</x:v>
@@ -5210,10 +5210,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AJ34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK34" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AL34" s="12" t="s">
         <x:v>49</x:v>
@@ -5222,10 +5222,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AN34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AO34" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AP34" s="12" t="s">
         <x:v>49</x:v>
@@ -5234,10 +5234,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AR34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AS34" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AT34" s="12" t="s">
         <x:v>49</x:v>
@@ -5246,10 +5246,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AV34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AW34" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AX34" s="12" t="s">
         <x:v>49</x:v>
@@ -5258,25 +5258,25 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AZ34" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BA34" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BB34" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC34" s="12">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="BD34" s="12" t="s">
-        <x:v>101</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="BE34" s="12">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="BF34" s="12" t="s">
-        <x:v>101</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:58">
@@ -5284,16 +5284,16 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="B35" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C35" s="12">
         <x:v>23</x:v>
       </x:c>
       <x:c r="D35" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E35" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F35" s="12" t="s">
         <x:v>49</x:v>
@@ -5302,10 +5302,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="H35" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I35" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J35" s="12" t="s">
         <x:v>49</x:v>
@@ -5326,10 +5326,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="P35" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q35" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R35" s="12" t="s">
         <x:v>49</x:v>
@@ -5338,10 +5338,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="T35" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U35" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V35" s="12" t="s">
         <x:v>49</x:v>
@@ -5350,22 +5350,22 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="X35" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y35" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z35" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AA35" s="12">
         <x:v>23</x:v>
       </x:c>
       <x:c r="AB35" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC35" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD35" s="12" t="s">
         <x:v>49</x:v>
@@ -5374,10 +5374,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AF35" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AG35" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH35" s="12" t="s">
         <x:v>49</x:v>
@@ -5386,10 +5386,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AJ35" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK35" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL35" s="12" t="s">
         <x:v>49</x:v>
@@ -5398,10 +5398,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AN35" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO35" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP35" s="12" t="s">
         <x:v>49</x:v>
@@ -5410,22 +5410,22 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AR35" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS35" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT35" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU35" s="12">
         <x:v>23</x:v>
       </x:c>
       <x:c r="AV35" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW35" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX35" s="12" t="s">
         <x:v>49</x:v>
@@ -5434,25 +5434,25 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AZ35" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BA35" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB35" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC35" s="12">
-        <x:v>52</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BD35" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="BE35" s="12">
-        <x:v>42</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BF35" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:58">
@@ -5460,16 +5460,16 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="B36" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C36" s="12">
         <x:v>24</x:v>
       </x:c>
       <x:c r="D36" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E36" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F36" s="12" t="s">
         <x:v>49</x:v>
@@ -5478,10 +5478,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H36" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I36" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J36" s="12" t="s">
         <x:v>49</x:v>
@@ -5502,7 +5502,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="P36" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q36" s="12" t="s">
         <x:v>57</x:v>
@@ -5514,7 +5514,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="T36" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U36" s="12" t="s">
         <x:v>54</x:v>
@@ -5526,19 +5526,19 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="X36" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y36" s="12" t="s">
         <x:v>58</x:v>
       </x:c>
       <x:c r="Z36" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AA36" s="12">
         <x:v>24</x:v>
       </x:c>
       <x:c r="AB36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC36" s="12" t="s">
         <x:v>49</x:v>
@@ -5550,10 +5550,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AF36" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AG36" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH36" s="12" t="s">
         <x:v>49</x:v>
@@ -5562,7 +5562,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AJ36" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK36" s="12" t="s">
         <x:v>49</x:v>
@@ -5574,10 +5574,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AN36" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO36" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AP36" s="12" t="s">
         <x:v>49</x:v>
@@ -5586,10 +5586,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AR36" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS36" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT36" s="12" t="s">
         <x:v>49</x:v>
@@ -5598,10 +5598,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AV36" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW36" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AX36" s="12" t="s">
         <x:v>49</x:v>
@@ -5610,25 +5610,25 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AZ36" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BA36" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB36" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC36" s="12">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="BD36" s="12" t="s">
         <x:v>104</x:v>
       </x:c>
       <x:c r="BE36" s="12">
-        <x:v>23</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="BF36" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:58">
@@ -5642,10 +5642,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="D37" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E37" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F37" s="12" t="s">
         <x:v>49</x:v>
@@ -5654,10 +5654,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="H37" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I37" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J37" s="12" t="s">
         <x:v>49</x:v>
@@ -5678,10 +5678,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="P37" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Q37" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="R37" s="12" t="s">
         <x:v>49</x:v>
@@ -5690,10 +5690,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="T37" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="U37" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="V37" s="12" t="s">
         <x:v>49</x:v>
@@ -5702,22 +5702,22 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="X37" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Y37" s="12" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="Z37" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AA37" s="12">
         <x:v>25</x:v>
       </x:c>
       <x:c r="AB37" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AC37" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AD37" s="12" t="s">
         <x:v>49</x:v>
@@ -5726,7 +5726,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AF37" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AG37" s="12" t="s">
         <x:v>54</x:v>
@@ -5738,10 +5738,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AJ37" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AK37" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AL37" s="12" t="s">
         <x:v>49</x:v>
@@ -5750,10 +5750,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AN37" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AO37" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AP37" s="12" t="s">
         <x:v>49</x:v>
@@ -5762,22 +5762,22 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AR37" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AS37" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT37" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU37" s="12">
         <x:v>25</x:v>
       </x:c>
       <x:c r="AV37" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AW37" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AX37" s="12" t="s">
         <x:v>49</x:v>
@@ -5786,25 +5786,25 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AZ37" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BA37" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BB37" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC37" s="12">
-        <x:v>19</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BD37" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="BE37" s="12">
-        <x:v>19</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="BF37" s="12" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:58">
@@ -5812,16 +5812,16 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="B38" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C38" s="12">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D38" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E38" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F38" s="12" t="s">
         <x:v>49</x:v>
@@ -5830,10 +5830,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="H38" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I38" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J38" s="12" t="s">
         <x:v>49</x:v>
@@ -5854,10 +5854,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="P38" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q38" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="R38" s="12" t="s">
         <x:v>49</x:v>
@@ -5866,10 +5866,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="T38" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U38" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V38" s="12" t="s">
         <x:v>49</x:v>
@@ -5878,19 +5878,19 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="X38" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y38" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Z38" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AA38" s="12">
         <x:v>26</x:v>
       </x:c>
       <x:c r="AB38" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AC38" s="12" t="s">
         <x:v>49</x:v>
@@ -5902,10 +5902,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AF38" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG38" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AH38" s="12" t="s">
         <x:v>49</x:v>
@@ -5914,7 +5914,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AJ38" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK38" s="12" t="s">
         <x:v>49</x:v>
@@ -5926,10 +5926,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AN38" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO38" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP38" s="12" t="s">
         <x:v>49</x:v>
@@ -5938,10 +5938,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AR38" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AS38" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AT38" s="12" t="s">
         <x:v>49</x:v>
@@ -5950,10 +5950,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AV38" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AW38" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AX38" s="12" t="s">
         <x:v>49</x:v>
@@ -5962,39 +5962,39 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AZ38" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BA38" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BB38" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC38" s="12">
-        <x:v>8</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="BD38" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BE38" s="12">
-        <x:v>8</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="BF38" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:58">
       <x:c r="A39" s="11" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B39" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C39" s="12">
         <x:v>27</x:v>
       </x:c>
       <x:c r="D39" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E39" s="12" t="s">
         <x:v>49</x:v>
@@ -6009,7 +6009,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="I39" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J39" s="12" t="s">
         <x:v>49</x:v>
@@ -6030,10 +6030,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="P39" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q39" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="R39" s="12" t="s">
         <x:v>49</x:v>
@@ -6042,10 +6042,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="T39" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="U39" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V39" s="12" t="s">
         <x:v>49</x:v>
@@ -6054,10 +6054,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="X39" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y39" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z39" s="12" t="s">
         <x:v>49</x:v>
@@ -6066,10 +6066,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AB39" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC39" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AD39" s="12" t="s">
         <x:v>49</x:v>
@@ -6078,10 +6078,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AF39" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AG39" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AH39" s="12" t="s">
         <x:v>49</x:v>
@@ -6090,10 +6090,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AJ39" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK39" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AL39" s="12" t="s">
         <x:v>49</x:v>
@@ -6102,7 +6102,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AN39" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AO39" s="12" t="s">
         <x:v>49</x:v>
@@ -6114,10 +6114,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AR39" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS39" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AT39" s="12" t="s">
         <x:v>49</x:v>
@@ -6126,10 +6126,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AV39" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AW39" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AX39" s="12" t="s">
         <x:v>49</x:v>
@@ -6138,25 +6138,25 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AZ39" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA39" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BB39" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC39" s="12">
-        <x:v>2</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="BD39" s="12" t="s">
-        <x:v>108</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BE39" s="12">
-        <x:v>2</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="BF39" s="12" t="s">
-        <x:v>108</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:58">
@@ -6170,7 +6170,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="D40" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E40" s="12" t="s">
         <x:v>49</x:v>
@@ -6185,7 +6185,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="I40" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J40" s="12" t="s">
         <x:v>49</x:v>
@@ -6206,10 +6206,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="P40" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Q40" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="R40" s="12" t="s">
         <x:v>49</x:v>
@@ -6218,10 +6218,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="T40" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U40" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V40" s="12" t="s">
         <x:v>49</x:v>
@@ -6233,19 +6233,19 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="Y40" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z40" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AA40" s="12">
         <x:v>28</x:v>
       </x:c>
       <x:c r="AB40" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AC40" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AD40" s="12" t="s">
         <x:v>49</x:v>
@@ -6257,7 +6257,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AG40" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AH40" s="12" t="s">
         <x:v>49</x:v>
@@ -6266,10 +6266,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AJ40" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK40" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AL40" s="12" t="s">
         <x:v>49</x:v>
@@ -6278,10 +6278,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AN40" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AO40" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP40" s="12" t="s">
         <x:v>49</x:v>
@@ -6293,7 +6293,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="AS40" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT40" s="12" t="s">
         <x:v>49</x:v>
@@ -6302,7 +6302,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AV40" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW40" s="12" t="s">
         <x:v>48</x:v>
@@ -6314,30 +6314,30 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AZ40" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BA40" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB40" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC40" s="12">
-        <x:v>46</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="BD40" s="12" t="s">
-        <x:v>110</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="BE40" s="12">
-        <x:v>43</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="BF40" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:58">
       <x:c r="A41" s="11" t="s">
-        <x:v>111</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B41" s="12" t="s">
         <x:v>63</x:v>
@@ -6349,7 +6349,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="E41" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F41" s="12" t="s">
         <x:v>49</x:v>
@@ -6361,7 +6361,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I41" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J41" s="12" t="s">
         <x:v>49</x:v>
@@ -6385,7 +6385,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="Q41" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R41" s="12" t="s">
         <x:v>49</x:v>
@@ -6397,7 +6397,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="U41" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V41" s="12" t="s">
         <x:v>49</x:v>
@@ -6409,7 +6409,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="Y41" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z41" s="12" t="s">
         <x:v>49</x:v>
@@ -6421,7 +6421,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AC41" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD41" s="12" t="s">
         <x:v>49</x:v>
@@ -6433,7 +6433,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AG41" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH41" s="12" t="s">
         <x:v>49</x:v>
@@ -6445,7 +6445,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AK41" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL41" s="12" t="s">
         <x:v>49</x:v>
@@ -6457,7 +6457,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AO41" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AP41" s="12" t="s">
         <x:v>49</x:v>
@@ -6469,7 +6469,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AS41" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AT41" s="12" t="s">
         <x:v>49</x:v>
@@ -6481,7 +6481,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AW41" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AX41" s="12" t="s">
         <x:v>49</x:v>
@@ -6493,36 +6493,36 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BA41" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB41" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC41" s="12">
-        <x:v>32</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="BD41" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="BE41" s="12">
-        <x:v>32</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="BF41" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:58">
       <x:c r="A42" s="11" t="s">
-        <x:v>112</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B42" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C42" s="12">
         <x:v>30</x:v>
       </x:c>
       <x:c r="D42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E42" s="12" t="s">
         <x:v>49</x:v>
@@ -6534,7 +6534,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="H42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I42" s="12" t="s">
         <x:v>49</x:v>
@@ -6558,10 +6558,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="P42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Q42" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R42" s="12" t="s">
         <x:v>49</x:v>
@@ -6570,7 +6570,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="T42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U42" s="12" t="s">
         <x:v>49</x:v>
@@ -6582,7 +6582,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="X42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Y42" s="12" t="s">
         <x:v>49</x:v>
@@ -6594,7 +6594,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AB42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC42" s="12" t="s">
         <x:v>49</x:v>
@@ -6606,7 +6606,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AF42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG42" s="12" t="s">
         <x:v>49</x:v>
@@ -6618,7 +6618,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AJ42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK42" s="12" t="s">
         <x:v>49</x:v>
@@ -6630,7 +6630,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AN42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO42" s="12" t="s">
         <x:v>49</x:v>
@@ -6642,10 +6642,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AR42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AS42" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT42" s="12" t="s">
         <x:v>49</x:v>
@@ -6654,7 +6654,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AV42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AW42" s="12" t="s">
         <x:v>49</x:v>
@@ -6666,7 +6666,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AZ42" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BA42" s="12" t="s">
         <x:v>49</x:v>
@@ -6675,16 +6675,16 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC42" s="12">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BD42" s="12" t="s">
-        <x:v>99</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BE42" s="12">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BF42" s="12" t="s">
-        <x:v>99</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:58">
@@ -6692,16 +6692,16 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="B43" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="D43" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F43" s="12" t="s">
         <x:v>49</x:v>
@@ -6710,10 +6710,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="H43" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I43" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J43" s="12" t="s">
         <x:v>49</x:v>
@@ -6734,10 +6734,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="P43" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q43" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="R43" s="12" t="s">
         <x:v>49</x:v>
@@ -6746,10 +6746,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="T43" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="U43" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="V43" s="12" t="s">
         <x:v>49</x:v>
@@ -6758,22 +6758,22 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="X43" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Z43" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AA43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="AB43" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AD43" s="12" t="s">
         <x:v>49</x:v>
@@ -6782,10 +6782,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AF43" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AG43" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AH43" s="12" t="s">
         <x:v>49</x:v>
@@ -6794,10 +6794,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AJ43" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK43" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AL43" s="12" t="s">
         <x:v>49</x:v>
@@ -6806,10 +6806,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AN43" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO43" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AP43" s="12" t="s">
         <x:v>49</x:v>
@@ -6818,22 +6818,22 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AR43" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS43" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT43" s="12" t="s">
-        <x:v>114</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU43" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="AV43" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW43" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AX43" s="12" t="s">
         <x:v>49</x:v>
@@ -6842,33 +6842,33 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AZ43" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BA43" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BB43" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC43" s="12">
-        <x:v>29</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BD43" s="12" t="s">
-        <x:v>101</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="BE43" s="12">
-        <x:v>17</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="BF43" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:58">
       <x:c r="A44" s="11" t="s">
-        <x:v>115</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B44" s="12" t="s">
-        <x:v>116</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C44" s="12">
         <x:v>32</x:v>
@@ -6877,10 +6877,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="E44" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G44" s="12">
         <x:v>32</x:v>
@@ -6889,10 +6889,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="I44" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K44" s="12">
         <x:v>32</x:v>
@@ -6913,10 +6913,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="Q44" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="R44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="S44" s="12">
         <x:v>32</x:v>
@@ -6925,10 +6925,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="U44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="V44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="W44" s="12">
         <x:v>32</x:v>
@@ -6937,10 +6937,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="Y44" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Z44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AA44" s="12">
         <x:v>32</x:v>
@@ -6949,10 +6949,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AC44" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AD44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AE44" s="12">
         <x:v>32</x:v>
@@ -6961,10 +6961,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AG44" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AH44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AI44" s="12">
         <x:v>32</x:v>
@@ -6973,10 +6973,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AK44" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AL44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AM44" s="12">
         <x:v>32</x:v>
@@ -6985,10 +6985,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AO44" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ44" s="12">
         <x:v>32</x:v>
@@ -6997,10 +6997,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AS44" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AT44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AU44" s="12">
         <x:v>32</x:v>
@@ -7009,10 +7009,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AW44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AX44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AY44" s="12">
         <x:v>32</x:v>
@@ -7021,27 +7021,27 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="BA44" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BB44" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BC44" s="12">
-        <x:v>45</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BD44" s="12" t="s">
-        <x:v>110</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="BE44" s="12">
-        <x:v>45</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BF44" s="12" t="s">
-        <x:v>110</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:58">
       <x:c r="A45" s="11" t="s">
-        <x:v>117</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B45" s="12" t="s">
         <x:v>46</x:v>
@@ -7050,25 +7050,25 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="D45" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E45" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="H45" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I45" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K45" s="12">
         <x:v>33</x:v>
@@ -7086,138 +7086,138 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="P45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q45" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="R45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="S45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="T45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="V45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="W45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="X45" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y45" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Z45" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AA45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="AB45" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC45" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AD45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AE45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="AF45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AG45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AH45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AI45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="AJ45" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AL45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AM45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="AN45" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AP45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AQ45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="AR45" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS45" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AT45" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AU45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="AV45" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW45" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AX45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AY45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="AZ45" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BA45" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BB45" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BC45" s="12">
-        <x:v>68</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BD45" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="BE45" s="12">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="BF45" s="12" t="s">
-        <x:v>119</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:58">
       <x:c r="A46" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B46" s="12" t="s">
         <x:v>46</x:v>
@@ -7226,10 +7226,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="D46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E46" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F46" s="12" t="s">
         <x:v>49</x:v>
@@ -7238,10 +7238,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="H46" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I46" s="12" t="s">
-        <x:v>114</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J46" s="12" t="s">
         <x:v>49</x:v>
@@ -7262,10 +7262,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="P46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Q46" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="R46" s="12" t="s">
         <x:v>49</x:v>
@@ -7274,34 +7274,34 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="T46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U46" s="12" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="V46" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="W46" s="12">
         <x:v>34</x:v>
       </x:c>
       <x:c r="X46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Y46" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Z46" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AA46" s="12">
         <x:v>34</x:v>
       </x:c>
       <x:c r="AB46" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AC46" s="12" t="s">
-        <x:v>121</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AD46" s="12" t="s">
         <x:v>49</x:v>
@@ -7310,10 +7310,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AF46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG46" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AH46" s="12" t="s">
         <x:v>49</x:v>
@@ -7322,10 +7322,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AJ46" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AK46" s="12" t="s">
-        <x:v>121</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AL46" s="12" t="s">
         <x:v>49</x:v>
@@ -7334,78 +7334,78 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="AN46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO46" s="12" t="s">
-        <x:v>122</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AP46" s="12" t="s">
-        <x:v>122</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ46" s="12">
         <x:v>34</x:v>
       </x:c>
       <x:c r="AR46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AS46" s="12" t="s">
-        <x:v>121</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT46" s="12" t="s">
-        <x:v>121</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU46" s="12">
         <x:v>34</x:v>
       </x:c>
       <x:c r="AV46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AW46" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AX46" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AY46" s="12">
         <x:v>34</x:v>
       </x:c>
       <x:c r="AZ46" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BA46" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BB46" s="12" t="s">
-        <x:v>118</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC46" s="12">
-        <x:v>164</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="BD46" s="12" t="s">
-        <x:v>123</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="BE46" s="12">
-        <x:v>81</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="BF46" s="12" t="s">
-        <x:v>124</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:58">
       <x:c r="A47" s="11" t="s">
-        <x:v>125</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B47" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C47" s="12">
         <x:v>35</x:v>
       </x:c>
       <x:c r="D47" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E47" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F47" s="12" t="s">
         <x:v>49</x:v>
@@ -7414,7 +7414,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="H47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I47" s="12" t="s">
         <x:v>54</x:v>
@@ -7438,10 +7438,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="P47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q47" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="R47" s="12" t="s">
         <x:v>49</x:v>
@@ -7450,7 +7450,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="T47" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U47" s="12" t="s">
         <x:v>54</x:v>
@@ -7462,22 +7462,22 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="X47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y47" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Z47" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AA47" s="12">
         <x:v>35</x:v>
       </x:c>
       <x:c r="AB47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC47" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AD47" s="12" t="s">
         <x:v>49</x:v>
@@ -7486,10 +7486,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AF47" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AG47" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AH47" s="12" t="s">
         <x:v>49</x:v>
@@ -7498,10 +7498,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AJ47" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK47" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AL47" s="12" t="s">
         <x:v>49</x:v>
@@ -7510,10 +7510,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AN47" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO47" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AP47" s="12" t="s">
         <x:v>49</x:v>
@@ -7522,22 +7522,22 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AR47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS47" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT47" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU47" s="12">
         <x:v>35</x:v>
       </x:c>
       <x:c r="AV47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW47" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AX47" s="12" t="s">
         <x:v>49</x:v>
@@ -7546,42 +7546,42 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="AZ47" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BA47" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BB47" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC47" s="12">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="BD47" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="BE47" s="12">
-        <x:v>13</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="BF47" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:58">
       <x:c r="A48" s="11" t="s">
-        <x:v>126</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B48" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="D48" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E48" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F48" s="12" t="s">
         <x:v>49</x:v>
@@ -7590,10 +7590,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="H48" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I48" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J48" s="12" t="s">
         <x:v>49</x:v>
@@ -7614,10 +7614,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="P48" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q48" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="R48" s="12" t="s">
         <x:v>49</x:v>
@@ -7626,10 +7626,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="T48" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U48" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V48" s="12" t="s">
         <x:v>49</x:v>
@@ -7638,22 +7638,22 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="X48" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y48" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z48" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AA48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="AB48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC48" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD48" s="12" t="s">
         <x:v>49</x:v>
@@ -7662,10 +7662,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AF48" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AG48" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH48" s="12" t="s">
         <x:v>49</x:v>
@@ -7674,10 +7674,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AJ48" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK48" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL48" s="12" t="s">
         <x:v>49</x:v>
@@ -7686,10 +7686,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AN48" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO48" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP48" s="12" t="s">
         <x:v>49</x:v>
@@ -7698,22 +7698,22 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AR48" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS48" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT48" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU48" s="12">
         <x:v>36</x:v>
       </x:c>
       <x:c r="AV48" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW48" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX48" s="12" t="s">
         <x:v>49</x:v>
@@ -7722,7 +7722,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="AZ48" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BA48" s="12" t="s">
         <x:v>49</x:v>
@@ -7731,21 +7731,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC48" s="12">
-        <x:v>28</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BD48" s="12" t="s">
-        <x:v>101</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="BE48" s="12">
-        <x:v>23</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BF48" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:58">
       <x:c r="A49" s="11" t="s">
-        <x:v>127</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B49" s="12" t="s">
         <x:v>46</x:v>
@@ -7754,10 +7754,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="D49" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E49" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F49" s="12" t="s">
         <x:v>49</x:v>
@@ -7766,7 +7766,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="H49" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I49" s="12" t="s">
         <x:v>58</x:v>
@@ -7790,10 +7790,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="P49" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Q49" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="R49" s="12" t="s">
         <x:v>49</x:v>
@@ -7802,7 +7802,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="T49" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="U49" s="12" t="s">
         <x:v>57</x:v>
@@ -7814,22 +7814,22 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="X49" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Y49" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Z49" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AA49" s="12">
         <x:v>37</x:v>
       </x:c>
       <x:c r="AB49" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC49" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD49" s="12" t="s">
         <x:v>49</x:v>
@@ -7841,7 +7841,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AG49" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AH49" s="12" t="s">
         <x:v>49</x:v>
@@ -7850,10 +7850,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AJ49" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK49" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AL49" s="12" t="s">
         <x:v>49</x:v>
@@ -7862,10 +7862,10 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AN49" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AO49" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP49" s="12" t="s">
         <x:v>49</x:v>
@@ -7874,22 +7874,22 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="AR49" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AS49" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="AT49" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="AU49" s="12">
         <x:v>37</x:v>
       </x:c>
       <x:c r="AV49" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW49" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AX49" s="12" t="s">
         <x:v>49</x:v>
@@ -7901,39 +7901,39 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="BA49" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB49" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC49" s="12">
-        <x:v>47</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="BD49" s="12" t="s">
-        <x:v>110</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="BE49" s="12">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="BF49" s="12" t="s">
-        <x:v>128</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:58">
       <x:c r="A50" s="11" t="s">
-        <x:v>129</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B50" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C50" s="12">
         <x:v>38</x:v>
       </x:c>
       <x:c r="D50" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F50" s="12" t="s">
         <x:v>49</x:v>
@@ -7942,10 +7942,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="H50" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J50" s="12" t="s">
         <x:v>49</x:v>
@@ -7966,10 +7966,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="P50" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="R50" s="12" t="s">
         <x:v>49</x:v>
@@ -7978,7 +7978,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="T50" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U50" s="12" t="s">
         <x:v>53</x:v>
@@ -7990,10 +7990,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="X50" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y50" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Z50" s="12" t="s">
         <x:v>49</x:v>
@@ -8002,7 +8002,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AB50" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC50" s="12" t="s">
         <x:v>54</x:v>
@@ -8014,10 +8014,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AF50" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AG50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AH50" s="12" t="s">
         <x:v>49</x:v>
@@ -8026,7 +8026,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AJ50" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK50" s="12" t="s">
         <x:v>54</x:v>
@@ -8038,10 +8038,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AN50" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO50" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP50" s="12" t="s">
         <x:v>49</x:v>
@@ -8050,10 +8050,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AR50" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT50" s="12" t="s">
         <x:v>49</x:v>
@@ -8062,10 +8062,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AV50" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AX50" s="12" t="s">
         <x:v>49</x:v>
@@ -8074,42 +8074,42 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="AZ50" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BA50" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BB50" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC50" s="12">
-        <x:v>16</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="BD50" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="BE50" s="12">
-        <x:v>16</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="BF50" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:58">
       <x:c r="A51" s="11" t="s">
-        <x:v>130</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B51" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C51" s="12">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D51" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E51" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F51" s="12" t="s">
         <x:v>49</x:v>
@@ -8118,10 +8118,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="H51" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I51" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J51" s="12" t="s">
         <x:v>49</x:v>
@@ -8142,10 +8142,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="P51" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Q51" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="R51" s="12" t="s">
         <x:v>49</x:v>
@@ -8154,10 +8154,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="T51" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="U51" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="V51" s="12" t="s">
         <x:v>49</x:v>
@@ -8166,22 +8166,22 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="X51" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Y51" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Z51" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AA51" s="12">
         <x:v>39</x:v>
       </x:c>
       <x:c r="AB51" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC51" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AD51" s="12" t="s">
         <x:v>49</x:v>
@@ -8190,10 +8190,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AF51" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG51" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AH51" s="12" t="s">
         <x:v>49</x:v>
@@ -8202,10 +8202,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AJ51" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AK51" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AL51" s="12" t="s">
         <x:v>49</x:v>
@@ -8214,7 +8214,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AN51" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO51" s="12" t="s">
         <x:v>53</x:v>
@@ -8226,22 +8226,22 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AR51" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AS51" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="AT51" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="AU51" s="12">
         <x:v>39</x:v>
       </x:c>
       <x:c r="AV51" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW51" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AX51" s="12" t="s">
         <x:v>49</x:v>
@@ -8250,7 +8250,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="AZ51" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="BA51" s="12" t="s">
         <x:v>54</x:v>
@@ -8259,33 +8259,33 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC51" s="12">
-        <x:v>33</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="BD51" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="BE51" s="12">
-        <x:v>28</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BF51" s="12" t="s">
-        <x:v>101</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:58">
       <x:c r="A52" s="11" t="s">
-        <x:v>131</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B52" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C52" s="12">
         <x:v>40</x:v>
       </x:c>
       <x:c r="D52" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E52" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="F52" s="12" t="s">
         <x:v>49</x:v>
@@ -8294,10 +8294,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="H52" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I52" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="J52" s="12" t="s">
         <x:v>49</x:v>
@@ -8318,10 +8318,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="P52" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q52" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="R52" s="12" t="s">
         <x:v>49</x:v>
@@ -8330,25 +8330,25 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="T52" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="U52" s="12" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="V52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="W52" s="12">
         <x:v>40</x:v>
       </x:c>
       <x:c r="X52" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Y52" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA52" s="12">
         <x:v>40</x:v>
@@ -8357,7 +8357,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AC52" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="AD52" s="12" t="s">
         <x:v>49</x:v>
@@ -8366,10 +8366,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AF52" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AG52" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AH52" s="12" t="s">
         <x:v>49</x:v>
@@ -8378,10 +8378,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AJ52" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AK52" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="AL52" s="12" t="s">
         <x:v>49</x:v>
@@ -8390,61 +8390,61 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="AN52" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AO52" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="AP52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="AQ52" s="12">
         <x:v>40</x:v>
       </x:c>
       <x:c r="AR52" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AS52" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="AT52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="AU52" s="12">
         <x:v>40</x:v>
       </x:c>
       <x:c r="AV52" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW52" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AX52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="AY52" s="12">
         <x:v>40</x:v>
       </x:c>
       <x:c r="AZ52" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BA52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="BB52" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="BC52" s="12">
-        <x:v>49</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="BD52" s="12" t="s">
-        <x:v>119</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="BE52" s="12">
-        <x:v>49</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="BF52" s="12" t="s">
-        <x:v>119</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:58">
@@ -8458,10 +8458,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="D53" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E53" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F53" s="12" t="s">
         <x:v>49</x:v>
@@ -8470,10 +8470,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="H53" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I53" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J53" s="12" t="s">
         <x:v>49</x:v>
@@ -8494,10 +8494,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="P53" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Q53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="R53" s="12" t="s">
         <x:v>49</x:v>
@@ -8506,10 +8506,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="T53" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U53" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V53" s="12" t="s">
         <x:v>49</x:v>
@@ -8518,22 +8518,22 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="X53" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Y53" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Z53" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AA53" s="12">
         <x:v>41</x:v>
       </x:c>
       <x:c r="AB53" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AC53" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD53" s="12" t="s">
         <x:v>49</x:v>
@@ -8542,10 +8542,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AF53" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG53" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH53" s="12" t="s">
         <x:v>49</x:v>
@@ -8554,10 +8554,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AJ53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AK53" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AL53" s="12" t="s">
         <x:v>49</x:v>
@@ -8569,7 +8569,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AO53" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP53" s="12" t="s">
         <x:v>49</x:v>
@@ -8578,22 +8578,22 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AR53" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AS53" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AU53" s="12">
         <x:v>41</x:v>
       </x:c>
       <x:c r="AV53" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW53" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AX53" s="12" t="s">
         <x:v>49</x:v>
@@ -8602,25 +8602,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="AZ53" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BA53" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB53" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC53" s="12">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="BD53" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="BE53" s="12">
-        <x:v>47</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="BF53" s="12" t="s">
-        <x:v>110</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:58">
@@ -8634,10 +8634,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="D54" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E54" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F54" s="12" t="s">
         <x:v>49</x:v>
@@ -8649,7 +8649,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="I54" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J54" s="12" t="s">
         <x:v>49</x:v>
@@ -8670,7 +8670,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="P54" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Q54" s="12" t="s">
         <x:v>58</x:v>
@@ -8682,10 +8682,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="T54" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U54" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="V54" s="12" t="s">
         <x:v>49</x:v>
@@ -8694,22 +8694,22 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="X54" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Y54" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Z54" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AA54" s="12">
         <x:v>42</x:v>
       </x:c>
       <x:c r="AB54" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AC54" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AD54" s="12" t="s">
         <x:v>49</x:v>
@@ -8718,10 +8718,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AF54" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG54" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AH54" s="12" t="s">
         <x:v>49</x:v>
@@ -8730,10 +8730,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AJ54" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK54" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AL54" s="12" t="s">
         <x:v>49</x:v>
@@ -8742,10 +8742,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AN54" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AO54" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AP54" s="12" t="s">
         <x:v>49</x:v>
@@ -8754,22 +8754,22 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AR54" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AS54" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT54" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AU54" s="12">
         <x:v>42</x:v>
       </x:c>
       <x:c r="AV54" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW54" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AX54" s="12" t="s">
         <x:v>49</x:v>
@@ -8778,7 +8778,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="AZ54" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BA54" s="12" t="s">
         <x:v>49</x:v>
@@ -8787,16 +8787,16 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC54" s="12">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="BD54" s="12" t="s">
         <x:v>104</x:v>
       </x:c>
       <x:c r="BE54" s="12">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="BF54" s="12" t="s">
-        <x:v>104</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:58">
@@ -8810,10 +8810,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="D55" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E55" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F55" s="12" t="s">
         <x:v>49</x:v>
@@ -8846,10 +8846,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="P55" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Q55" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="R55" s="12" t="s">
         <x:v>49</x:v>
@@ -8861,7 +8861,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="U55" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="V55" s="12" t="s">
         <x:v>49</x:v>
@@ -8870,19 +8870,19 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="X55" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Y55" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Z55" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AA55" s="12">
         <x:v>43</x:v>
       </x:c>
       <x:c r="AB55" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AC55" s="12" t="s">
         <x:v>54</x:v>
@@ -8894,10 +8894,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AF55" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG55" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AH55" s="12" t="s">
         <x:v>49</x:v>
@@ -8906,7 +8906,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AJ55" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK55" s="12" t="s">
         <x:v>57</x:v>
@@ -8918,10 +8918,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AN55" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AO55" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AP55" s="12" t="s">
         <x:v>49</x:v>
@@ -8930,19 +8930,19 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="AR55" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AS55" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT55" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU55" s="12">
         <x:v>43</x:v>
       </x:c>
       <x:c r="AV55" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AW55" s="12" t="s">
         <x:v>58</x:v>
@@ -8957,27 +8957,27 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="BA55" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BB55" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC55" s="12">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="BD55" s="12" t="s">
-        <x:v>80</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="BE55" s="12">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="BF55" s="12" t="s">
-        <x:v>73</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:58">
       <x:c r="A56" s="11" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B56" s="12" t="s">
         <x:v>46</x:v>
@@ -8986,10 +8986,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="D56" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E56" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F56" s="12" t="s">
         <x:v>49</x:v>
@@ -8998,10 +8998,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="H56" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I56" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J56" s="12" t="s">
         <x:v>49</x:v>
@@ -9025,7 +9025,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="Q56" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R56" s="12" t="s">
         <x:v>49</x:v>
@@ -9034,7 +9034,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="T56" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U56" s="12" t="s">
         <x:v>53</x:v>
@@ -9049,7 +9049,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="Y56" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Z56" s="12" t="s">
         <x:v>49</x:v>
@@ -9058,10 +9058,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AB56" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AC56" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AD56" s="12" t="s">
         <x:v>49</x:v>
@@ -9070,10 +9070,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AF56" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG56" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH56" s="12" t="s">
         <x:v>49</x:v>
@@ -9082,10 +9082,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AJ56" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AK56" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AL56" s="12" t="s">
         <x:v>49</x:v>
@@ -9094,10 +9094,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AN56" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO56" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AP56" s="12" t="s">
         <x:v>49</x:v>
@@ -9106,22 +9106,22 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="AR56" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AS56" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT56" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU56" s="12">
         <x:v>44</x:v>
       </x:c>
       <x:c r="AV56" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AW56" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX56" s="12" t="s">
         <x:v>49</x:v>
@@ -9133,39 +9133,39 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="BA56" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB56" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC56" s="12">
-        <x:v>53</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="BD56" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="BE56" s="12">
-        <x:v>49</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="BF56" s="12" t="s">
-        <x:v>119</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:58">
       <x:c r="A57" s="11" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B57" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C57" s="12">
         <x:v>45</x:v>
       </x:c>
       <x:c r="D57" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E57" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F57" s="12" t="s">
         <x:v>49</x:v>
@@ -9174,10 +9174,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="H57" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I57" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J57" s="12" t="s">
         <x:v>49</x:v>
@@ -9201,7 +9201,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="Q57" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="R57" s="12" t="s">
         <x:v>49</x:v>
@@ -9210,7 +9210,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="T57" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="U57" s="12" t="s">
         <x:v>57</x:v>
@@ -9222,22 +9222,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="X57" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Y57" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Z57" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AA57" s="12">
         <x:v>45</x:v>
       </x:c>
       <x:c r="AB57" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC57" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AD57" s="12" t="s">
         <x:v>49</x:v>
@@ -9246,10 +9246,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AF57" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AG57" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH57" s="12" t="s">
         <x:v>49</x:v>
@@ -9258,10 +9258,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AJ57" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK57" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AL57" s="12" t="s">
         <x:v>49</x:v>
@@ -9270,10 +9270,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AN57" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AO57" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AP57" s="12" t="s">
         <x:v>49</x:v>
@@ -9285,19 +9285,19 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="AS57" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AT57" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AU57" s="12">
         <x:v>45</x:v>
       </x:c>
       <x:c r="AV57" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AW57" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AX57" s="12" t="s">
         <x:v>49</x:v>
@@ -9306,7 +9306,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AZ57" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BA57" s="12" t="s">
         <x:v>54</x:v>
@@ -9315,33 +9315,33 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC57" s="12">
-        <x:v>53</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="BD57" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="BE57" s="12">
-        <x:v>41</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="BF57" s="12" t="s">
-        <x:v>72</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:58">
       <x:c r="A58" s="11" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B58" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C58" s="12">
         <x:v>46</x:v>
       </x:c>
       <x:c r="D58" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E58" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F58" s="12" t="s">
         <x:v>49</x:v>
@@ -9350,10 +9350,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H58" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I58" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J58" s="12" t="s">
         <x:v>49</x:v>
@@ -9374,10 +9374,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="P58" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Q58" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R58" s="12" t="s">
         <x:v>49</x:v>
@@ -9386,10 +9386,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="T58" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="U58" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V58" s="12" t="s">
         <x:v>49</x:v>
@@ -9398,19 +9398,19 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="X58" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y58" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z58" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AA58" s="12">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AB58" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC58" s="12" t="s">
         <x:v>49</x:v>
@@ -9422,7 +9422,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AF58" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AG58" s="12" t="s">
         <x:v>49</x:v>
@@ -9446,10 +9446,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AN58" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AO58" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP58" s="12" t="s">
         <x:v>49</x:v>
@@ -9458,22 +9458,22 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AR58" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS58" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AT58" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU58" s="12">
         <x:v>46</x:v>
       </x:c>
       <x:c r="AV58" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW58" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX58" s="12" t="s">
         <x:v>49</x:v>
@@ -9482,42 +9482,42 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AZ58" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BA58" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="BB58" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC58" s="12">
-        <x:v>23</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="BD58" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="BE58" s="12">
-        <x:v>15</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="BF58" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:58">
       <x:c r="A59" s="11" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B59" s="12" t="s">
-        <x:v>46</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C59" s="12">
         <x:v>47</x:v>
       </x:c>
       <x:c r="D59" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E59" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F59" s="12" t="s">
         <x:v>49</x:v>
@@ -9526,7 +9526,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="H59" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I59" s="12" t="s">
         <x:v>48</x:v>
@@ -9550,10 +9550,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="P59" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q59" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="R59" s="12" t="s">
         <x:v>49</x:v>
@@ -9562,10 +9562,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="T59" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U59" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="V59" s="12" t="s">
         <x:v>49</x:v>
@@ -9574,10 +9574,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="X59" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y59" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Z59" s="12" t="s">
         <x:v>49</x:v>
@@ -9586,10 +9586,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AB59" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AC59" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AD59" s="12" t="s">
         <x:v>49</x:v>
@@ -9598,10 +9598,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AF59" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AG59" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AH59" s="12" t="s">
         <x:v>49</x:v>
@@ -9610,10 +9610,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AJ59" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AK59" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AL59" s="12" t="s">
         <x:v>49</x:v>
@@ -9622,10 +9622,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AN59" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AO59" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AP59" s="12" t="s">
         <x:v>49</x:v>
@@ -9634,10 +9634,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AR59" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS59" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT59" s="12" t="s">
         <x:v>49</x:v>
@@ -9646,10 +9646,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AV59" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AW59" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AX59" s="12" t="s">
         <x:v>49</x:v>
@@ -9658,7 +9658,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="AZ59" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="BA59" s="12" t="s">
         <x:v>49</x:v>
@@ -9667,21 +9667,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC59" s="12">
-        <x:v>17</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BD59" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="BE59" s="12">
-        <x:v>17</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF59" s="12" t="s">
-        <x:v>77</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:58">
       <x:c r="A60" s="11" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B60" s="12" t="s">
         <x:v>46</x:v>
@@ -9690,10 +9690,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D60" s="12" t="s">
-        <x:v>79</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E60" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F60" s="12" t="s">
         <x:v>49</x:v>
@@ -9702,10 +9702,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H60" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I60" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J60" s="12" t="s">
         <x:v>49</x:v>
@@ -9726,10 +9726,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="P60" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Q60" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="R60" s="12" t="s">
         <x:v>49</x:v>
@@ -9738,7 +9738,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="T60" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="U60" s="12" t="s">
         <x:v>49</x:v>
@@ -9750,10 +9750,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="X60" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Y60" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z60" s="12" t="s">
         <x:v>49</x:v>
@@ -9762,10 +9762,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AB60" s="12" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="AC60" s="12" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="AC60" s="12" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="AD60" s="12" t="s">
         <x:v>49</x:v>
@@ -9777,7 +9777,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AG60" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AH60" s="12" t="s">
         <x:v>49</x:v>
@@ -9786,10 +9786,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AJ60" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK60" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="AL60" s="12" t="s">
         <x:v>49</x:v>
@@ -9801,7 +9801,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="AO60" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="AP60" s="12" t="s">
         <x:v>49</x:v>
@@ -9810,13 +9810,13 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AR60" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AS60" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AT60" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AU60" s="12">
         <x:v>48</x:v>
@@ -9825,7 +9825,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AW60" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AX60" s="12" t="s">
         <x:v>49</x:v>
@@ -9834,30 +9834,30 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AZ60" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BA60" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="BB60" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC60" s="12">
-        <x:v>1</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BD60" s="12" t="s">
-        <x:v>99</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="BE60" s="12">
-        <x:v>1</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="BF60" s="12" t="s">
-        <x:v>99</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:58">
       <x:c r="A61" s="11" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B61" s="12" t="s">
         <x:v>46</x:v>
@@ -9866,10 +9866,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="D61" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E61" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F61" s="12" t="s">
         <x:v>49</x:v>
@@ -9881,7 +9881,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="I61" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J61" s="12" t="s">
         <x:v>49</x:v>
@@ -9902,10 +9902,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="P61" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Q61" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="R61" s="12" t="s">
         <x:v>49</x:v>
@@ -9914,7 +9914,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="T61" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="U61" s="12" t="s">
         <x:v>49</x:v>
@@ -9926,10 +9926,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="X61" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Y61" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Z61" s="12" t="s">
         <x:v>49</x:v>
@@ -9938,7 +9938,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AB61" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AC61" s="12" t="s">
         <x:v>49</x:v>
@@ -9950,10 +9950,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AF61" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AG61" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AH61" s="12" t="s">
         <x:v>49</x:v>
@@ -9965,7 +9965,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="AK61" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AL61" s="12" t="s">
         <x:v>49</x:v>
@@ -9974,10 +9974,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AN61" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AO61" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AP61" s="12" t="s">
         <x:v>49</x:v>
@@ -9986,10 +9986,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AR61" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AS61" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT61" s="12" t="s">
         <x:v>49</x:v>
@@ -9998,10 +9998,10 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AV61" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AW61" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AX61" s="12" t="s">
         <x:v>49</x:v>
@@ -10010,7 +10010,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AZ61" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BA61" s="12" t="s">
         <x:v>49</x:v>
@@ -10019,33 +10019,33 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC61" s="12">
-        <x:v>2</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="BD61" s="12" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="BE61" s="12">
-        <x:v>2</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="BF61" s="12" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:58">
       <x:c r="A62" s="11" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B62" s="12" t="s">
-        <x:v>85</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D62" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E62" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F62" s="12" t="s">
         <x:v>49</x:v>
@@ -10054,10 +10054,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H62" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I62" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J62" s="12" t="s">
         <x:v>49</x:v>
@@ -10081,7 +10081,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="Q62" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="R62" s="12" t="s">
         <x:v>49</x:v>
@@ -10090,10 +10090,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="T62" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U62" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="V62" s="12" t="s">
         <x:v>49</x:v>
@@ -10102,22 +10102,22 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="X62" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Y62" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AA62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="AB62" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AC62" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AD62" s="12" t="s">
         <x:v>49</x:v>
@@ -10126,10 +10126,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AF62" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG62" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AH62" s="12" t="s">
         <x:v>49</x:v>
@@ -10138,7 +10138,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AJ62" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AK62" s="12" t="s">
         <x:v>57</x:v>
@@ -10150,10 +10150,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AN62" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AO62" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AP62" s="12" t="s">
         <x:v>49</x:v>
@@ -10162,22 +10162,22 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AR62" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AS62" s="12" t="s">
-        <x:v>47</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="AT62" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="AU62" s="12">
         <x:v>50</x:v>
       </x:c>
       <x:c r="AV62" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW62" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AX62" s="12" t="s">
         <x:v>49</x:v>
@@ -10186,90 +10186,90 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AZ62" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BA62" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB62" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC62" s="12">
-        <x:v>60</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="BD62" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="BE62" s="12">
-        <x:v>60</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="BF62" s="12" t="s">
-        <x:v>68</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:58">
       <x:c r="A63" s="11" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B63" s="12" t="s">
-        <x:v>85</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C63" s="12">
         <x:v>51</x:v>
       </x:c>
       <x:c r="D63" s="12" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E63" s="12" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F63" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G63" s="12">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H63" s="12" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="I63" s="12" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="J63" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="K63" s="12">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="L63" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="M63" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="N63" s="12" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="O63" s="12">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="P63" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="Q63" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="R63" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="S63" s="12">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="T63" s="12" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="E63" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F63" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="G63" s="12">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="H63" s="12" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="I63" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="J63" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="K63" s="12">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="L63" s="12" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="M63" s="12" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="N63" s="12" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="O63" s="12">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="P63" s="12" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="Q63" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="R63" s="12" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="S63" s="12">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="T63" s="12" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="U63" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="V63" s="12" t="s">
         <x:v>49</x:v>
@@ -10278,10 +10278,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="X63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Y63" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Z63" s="12" t="s">
         <x:v>49</x:v>
@@ -10290,10 +10290,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AB63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AC63" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AD63" s="12" t="s">
         <x:v>49</x:v>
@@ -10302,10 +10302,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AF63" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AG63" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AH63" s="12" t="s">
         <x:v>49</x:v>
@@ -10314,10 +10314,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AJ63" s="12" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK63" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AL63" s="12" t="s">
         <x:v>49</x:v>
@@ -10326,10 +10326,10 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AN63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AO63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AP63" s="12" t="s">
         <x:v>49</x:v>
@@ -10338,22 +10338,22 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AR63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AS63" s="12" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="AT63" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AU63" s="12">
         <x:v>51</x:v>
       </x:c>
       <x:c r="AV63" s="12" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AW63" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AX63" s="12" t="s">
         <x:v>49</x:v>
@@ -10362,42 +10362,42 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AZ63" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="BA63" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="BB63" s="12" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC63" s="12">
-        <x:v>23</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BD63" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="BE63" s="12">
-        <x:v>23</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BF63" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:58">
       <x:c r="A64" s="11" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B64" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C64" s="12">
         <x:v>52</x:v>
       </x:c>
       <x:c r="D64" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E64" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F64" s="12" t="s">
         <x:v>49</x:v>
@@ -10406,10 +10406,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="H64" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I64" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J64" s="12" t="s">
         <x:v>49</x:v>
@@ -10430,10 +10430,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="P64" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Q64" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="R64" s="12" t="s">
         <x:v>49</x:v>
@@ -10442,10 +10442,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="T64" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="U64" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="V64" s="12" t="s">
         <x:v>49</x:v>
@@ -10454,22 +10454,22 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="X64" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Y64" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Z64" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AA64" s="12">
         <x:v>52</x:v>
       </x:c>
       <x:c r="AB64" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AC64" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AD64" s="12" t="s">
         <x:v>49</x:v>
@@ -10478,10 +10478,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AF64" s="12" t="s">
-        <x:v>51</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="AG64" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AH64" s="12" t="s">
         <x:v>49</x:v>
@@ -10490,10 +10490,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AJ64" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AK64" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AL64" s="12" t="s">
         <x:v>49</x:v>
@@ -10502,10 +10502,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AN64" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO64" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AP64" s="12" t="s">
         <x:v>49</x:v>
@@ -10514,19 +10514,19 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AR64" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AS64" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="AT64" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="AU64" s="12">
         <x:v>52</x:v>
       </x:c>
       <x:c r="AV64" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW64" s="12" t="s">
         <x:v>49</x:v>
@@ -10538,7 +10538,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="AZ64" s="12" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="BA64" s="12" t="s">
         <x:v>54</x:v>
@@ -10547,21 +10547,21 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="BC64" s="12">
-        <x:v>6</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BD64" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="BE64" s="12">
-        <x:v>6</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="BF64" s="12" t="s">
-        <x:v>64</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:58">
       <x:c r="A65" s="11" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B65" s="12" t="s">
         <x:v>46</x:v>
@@ -10570,25 +10570,25 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="D65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G65" s="12">
         <x:v>53</x:v>
       </x:c>
       <x:c r="H65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K65" s="12">
         <x:v>53</x:v>
@@ -10606,133 +10606,133 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="P65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Q65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="R65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S65" s="12">
         <x:v>53</x:v>
       </x:c>
       <x:c r="T65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="U65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="W65" s="12">
         <x:v>53</x:v>
       </x:c>
       <x:c r="X65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Y65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="Z65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AA65" s="12">
         <x:v>53</x:v>
       </x:c>
       <x:c r="AB65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="AC65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AE65" s="12">
         <x:v>53</x:v>
       </x:c>
       <x:c r="AF65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AI65" s="12">
         <x:v>53</x:v>
       </x:c>
       <x:c r="AJ65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM65" s="12">
         <x:v>53</x:v>
       </x:c>
       <x:c r="AN65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AO65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AP65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ65" s="12">
         <x:v>53</x:v>
       </x:c>
       <x:c r="AR65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AS65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AT65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AU65" s="12">
         <x:v>53</x:v>
       </x:c>
       <x:c r="AV65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AW65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AX65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AY65" s="12">
         <x:v>53</x:v>
       </x:c>
       <x:c r="AZ65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="BA65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB65" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC65" s="12">
-        <x:v>0</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="BD65" s="12" t="s">
-        <x:v>99</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="BE65" s="12">
-        <x:v>0</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="BF65" s="12" t="s">
-        <x:v>145</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:58">
@@ -10746,25 +10746,25 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="D66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G66" s="12">
         <x:v>54</x:v>
       </x:c>
       <x:c r="H66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K66" s="12">
         <x:v>54</x:v>
@@ -10782,133 +10782,133 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="P66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="Q66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S66" s="12">
         <x:v>54</x:v>
       </x:c>
       <x:c r="T66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="W66" s="12">
         <x:v>54</x:v>
       </x:c>
       <x:c r="X66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AA66" s="12">
         <x:v>54</x:v>
       </x:c>
       <x:c r="AB66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AC66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AD66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AE66" s="12">
         <x:v>54</x:v>
       </x:c>
       <x:c r="AF66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AI66" s="12">
         <x:v>54</x:v>
       </x:c>
       <x:c r="AJ66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AL66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM66" s="12">
         <x:v>54</x:v>
       </x:c>
       <x:c r="AN66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AO66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AP66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ66" s="12">
         <x:v>54</x:v>
       </x:c>
       <x:c r="AR66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AS66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU66" s="12">
         <x:v>54</x:v>
       </x:c>
       <x:c r="AV66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AW66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AY66" s="12">
         <x:v>54</x:v>
       </x:c>
       <x:c r="AZ66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="BA66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB66" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC66" s="12">
-        <x:v>0</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="BD66" s="12" t="s">
-        <x:v>99</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="BE66" s="12">
-        <x:v>0</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="BF66" s="12" t="s">
-        <x:v>145</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:58">
@@ -10922,25 +10922,25 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="D67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G67" s="12">
         <x:v>55</x:v>
       </x:c>
       <x:c r="H67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="I67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K67" s="12">
         <x:v>55</x:v>
@@ -10958,133 +10958,133 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Q67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S67" s="12">
         <x:v>55</x:v>
       </x:c>
       <x:c r="T67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="U67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="W67" s="12">
         <x:v>55</x:v>
       </x:c>
       <x:c r="X67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Y67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AA67" s="12">
         <x:v>55</x:v>
       </x:c>
       <x:c r="AB67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AE67" s="12">
         <x:v>55</x:v>
       </x:c>
       <x:c r="AF67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AG67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AI67" s="12">
         <x:v>55</x:v>
       </x:c>
       <x:c r="AJ67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AK67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM67" s="12">
         <x:v>55</x:v>
       </x:c>
       <x:c r="AN67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AO67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ67" s="12">
         <x:v>55</x:v>
       </x:c>
       <x:c r="AR67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AS67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU67" s="12">
         <x:v>55</x:v>
       </x:c>
       <x:c r="AV67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AW67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AY67" s="12">
         <x:v>55</x:v>
       </x:c>
       <x:c r="AZ67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="BA67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB67" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC67" s="12">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BD67" s="12" t="s">
-        <x:v>99</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="BE67" s="12">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="BF67" s="12" t="s">
-        <x:v>145</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:58">
@@ -11098,25 +11098,25 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="D68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G68" s="12">
         <x:v>56</x:v>
       </x:c>
       <x:c r="H68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="I68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K68" s="12">
         <x:v>56</x:v>
@@ -11134,133 +11134,133 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="P68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Q68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="R68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="S68" s="12">
         <x:v>56</x:v>
       </x:c>
       <x:c r="T68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="U68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="V68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="W68" s="12">
         <x:v>56</x:v>
       </x:c>
       <x:c r="X68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Y68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AA68" s="12">
         <x:v>56</x:v>
       </x:c>
       <x:c r="AB68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AC68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AD68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AE68" s="12">
         <x:v>56</x:v>
       </x:c>
       <x:c r="AF68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AG68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AH68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AI68" s="12">
         <x:v>56</x:v>
       </x:c>
       <x:c r="AJ68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AK68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AL68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AM68" s="12">
         <x:v>56</x:v>
       </x:c>
       <x:c r="AN68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AO68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AP68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AQ68" s="12">
         <x:v>56</x:v>
       </x:c>
       <x:c r="AR68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AS68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AU68" s="12">
         <x:v>56</x:v>
       </x:c>
       <x:c r="AV68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AW68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AX68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AY68" s="12">
         <x:v>56</x:v>
       </x:c>
       <x:c r="AZ68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="BA68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BB68" s="12" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="BC68" s="12">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BD68" s="12" t="s">
-        <x:v>99</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="BE68" s="12">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="BF68" s="12" t="s">
-        <x:v>145</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:58">
